--- a/extenbooks/S1507_extenbook.xlsx
+++ b/extenbooks/S1507_extenbook.xlsx
@@ -4781,7 +4781,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -5578,11 +5578,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5605,64 +5605,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Chapter 15 series S1507</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1507_research.json", "adequacy_report": "Technical/docs/chapters/CH15_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1507_DPR.md", "epr": "Technical/docs/series/S1507_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1507_load.py", "processor": "Technical/code/P02_processors/P02_S1507_construct.py", "validator": "Technical/code/V03_validators/V03_S1507_validate.py", "processed": "Technical/data/processed/S1507.parquet", "chopped_csv": "Technical/chopped/S1507.csv", "extenbook_xlsx": "Technical/extenbooks/S1507_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1507_extenbook.xlsx
+++ b/extenbooks/S1507_extenbook.xlsx
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>rate_decimal</t>
+          <t>normalized_zscore</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Pipeline stage**: Ingestion</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4839,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>**S1507** is the open historical sub-period of S1505: 1982-2010. Same subseries set, restricted to the post-Volcker era. Unlike S1506, this regime continues into the present and is therefore the natural forward-extension target — when S1505 is extended past 2010 (Phase 9+ work), S1507 should be extended in lockstep.</t>
+          <t>**S1507** is the open historical sub-period of S1505: 1982-2010. Same subseries set, restricted to the post-Volcker era. Unlike S1506, this regime continues into the present and is therefore the natural forward-extension target — when S1505 is extended past 2010 (future work), S1507 should be extended in lockstep.</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>**Phase**: 6 (Extension)</t>
+          <t>**Pipeline stage**: Extension</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>The post-Volcker regime continues into the present. When S1505 extension lands (BEA NIPA + BLS UNRATE re-fetched), S1507 inherits those extra years automatically — its loader just filters the parent.</t>
+          <t>The post-Volcker regime continues into the present. When the S1505 extension lands (U.S. Bureau of Economic Analysis National Income and Product Accounts (NIPA) data plus the BLS unemployment rate, FRED `UNRATE`, re-fetched), S1507 inherits those extra years automatically — its loader just filters the parent.</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-18T22:14:08.299085+00:00</t>
+          <t>2026-07-10T14:18:45.447583+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1507_extenbook.xlsx
+++ b/extenbooks/S1507_extenbook.xlsx
@@ -5563,7 +5563,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-10T14:18:45.447583+00:00</t>
+          <t>2026-07-11T03:44:23.452029+00:00</t>
         </is>
       </c>
     </row>
@@ -5578,11 +5578,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5605,6 +5605,150 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_2016_APPENDIX_15_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>derived_subperiod</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful derived sub-period of S1505 covering 1982-2010, replicating book figure 15.9 (post-Volcker/neoliberal regime). Construction-relevant companion to S1506: the chapter contrasts the two eras to show the downward shift of the classical inflation curve. Deterministic extendable slice of S1505. Per-subseries units split (sigma-prime normalized).", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1507_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1507_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>per_subseries</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
